--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81708FE-9AE6-4183-92EA-89434F4DA9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C1AC0F-2DBE-4831-9178-1043B4F2C7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7161" uniqueCount="3645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14322" uniqueCount="3645">
   <si>
     <t>CODIGO</t>
   </si>
@@ -12063,7 +12063,7 @@
         <v>12910</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8410D1-252D-4333-A7B2-11693505F8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66059558-DAE9-4AAE-A270-919EC4217069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7165" uniqueCount="3647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7166" uniqueCount="3648">
   <si>
     <t>CODIGO</t>
   </si>
@@ -10976,6 +10976,9 @@
   </si>
   <si>
     <t>AURICULAR INALAMBRICO CON POWER BANK JS-52</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
   </si>
 </sst>
 </file>
@@ -11854,7 +11857,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5E9BE6-5C02-4A6B-8DFA-EC1852FAD57E}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F3594"/>
+  <dimension ref="A1:G3594"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="60.42578125" bestFit="1" customWidth="1"/>
@@ -11862,7 +11865,7 @@
     <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11881,8 +11884,11 @@
       <c r="F1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>3909</v>
       </c>
@@ -11902,7 +11908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3908</v>
       </c>
@@ -11922,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3907</v>
       </c>
@@ -11942,7 +11948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3906</v>
       </c>
@@ -11962,7 +11968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3905</v>
       </c>
@@ -11982,7 +11988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3904</v>
       </c>
@@ -12002,7 +12008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3903</v>
       </c>
@@ -12022,7 +12028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3902</v>
       </c>
@@ -12042,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3901</v>
       </c>
@@ -12062,7 +12068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3900</v>
       </c>
@@ -12082,7 +12088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3899</v>
       </c>
@@ -12102,7 +12108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3898</v>
       </c>
@@ -12122,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3897</v>
       </c>
@@ -12142,7 +12148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3896</v>
       </c>
@@ -12162,7 +12168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3895</v>
       </c>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAA1502-3E78-4043-B333-60AC0B830F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F369AAC9-E43D-448B-A522-25CAA6424F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7E2E11-B8DE-4922-A1CC-5292AAB01854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE73D7B-297A-4177-8EAF-2380C65FF276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11014" uniqueCount="3739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11014" uniqueCount="3740">
   <si>
     <t>CODIGO</t>
   </si>
@@ -11251,6 +11251,9 @@
   </si>
   <si>
     <t>Microfono Dynamic Infantil TMMIC9814</t>
+  </si>
+  <si>
+    <t>Alcohol Isopropilico El Repa 500cc</t>
   </si>
 </sst>
 </file>
@@ -12163,19 +12166,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="B2" t="s">
-        <v>3735</v>
+        <v>3739</v>
       </c>
       <c r="C2">
-        <v>10500</v>
+        <v>22350</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>3480</v>
       </c>
       <c r="E2">
-        <v>8900</v>
+        <v>19000</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -12186,19 +12189,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="B3" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="C3">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="D3" t="s">
-        <v>3472</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>8500</v>
+        <v>8900</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -12209,19 +12212,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B4" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="C4">
-        <v>25100</v>
+        <v>10000</v>
       </c>
       <c r="D4" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="E4">
-        <v>21300</v>
+        <v>8500</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -12232,19 +12235,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="B5" t="s">
-        <v>3732</v>
+        <v>3737</v>
       </c>
       <c r="C5">
-        <v>10590</v>
+        <v>25100</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>3474</v>
       </c>
       <c r="E5">
-        <v>9000</v>
+        <v>21300</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -12255,22 +12258,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="B6" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="C6">
-        <v>4120</v>
+        <v>10590</v>
       </c>
       <c r="D6" t="s">
-        <v>3477</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>3500</v>
+        <v>9000</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>3495</v>
@@ -12278,22 +12281,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B7" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="C7">
-        <v>32940</v>
+        <v>4120</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>3477</v>
       </c>
       <c r="E7">
-        <v>28000</v>
+        <v>3500</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
         <v>3495</v>
@@ -12301,19 +12304,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="B8" t="s">
-        <v>3729</v>
+        <v>3734</v>
       </c>
       <c r="C8">
-        <v>22350</v>
+        <v>32940</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>19000</v>
+        <v>28000</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -12324,22 +12327,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3999</v>
+        <v>4000</v>
       </c>
       <c r="B9" t="s">
-        <v>3728</v>
+        <v>3729</v>
       </c>
       <c r="C9">
-        <v>32940</v>
+        <v>22350</v>
       </c>
       <c r="D9" t="s">
-        <v>3476</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>28000</v>
+        <v>19000</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="s">
         <v>3495</v>
@@ -12347,22 +12350,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3998</v>
+        <v>3999</v>
       </c>
       <c r="B10" t="s">
-        <v>3725</v>
+        <v>3728</v>
       </c>
       <c r="C10">
-        <v>9500</v>
+        <v>32940</v>
       </c>
       <c r="D10" t="s">
-        <v>3474</v>
+        <v>3476</v>
       </c>
       <c r="E10">
-        <v>8100</v>
+        <v>28000</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="s">
         <v>3495</v>
@@ -12370,22 +12373,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="B11" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="C11">
-        <v>25000</v>
+        <v>9500</v>
       </c>
       <c r="D11" t="s">
-        <v>3673</v>
+        <v>3474</v>
       </c>
       <c r="E11">
-        <v>21300</v>
+        <v>8100</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
         <v>3495</v>
@@ -12393,22 +12396,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3996</v>
+        <v>3997</v>
       </c>
       <c r="B12" t="s">
-        <v>3724</v>
+        <v>3726</v>
       </c>
       <c r="C12">
-        <v>35890</v>
+        <v>25000</v>
       </c>
       <c r="D12" t="s">
-        <v>3476</v>
+        <v>3673</v>
       </c>
       <c r="E12">
-        <v>30500</v>
+        <v>21300</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
         <v>3495</v>
@@ -12416,22 +12419,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3995</v>
+        <v>3996</v>
       </c>
       <c r="B13" t="s">
-        <v>3716</v>
+        <v>3724</v>
       </c>
       <c r="C13">
-        <v>10000</v>
+        <v>35890</v>
       </c>
       <c r="D13" t="s">
-        <v>3673</v>
+        <v>3476</v>
       </c>
       <c r="E13">
-        <v>8500</v>
+        <v>30500</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="s">
         <v>3495</v>
@@ -12439,22 +12442,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>3994</v>
+        <v>3995</v>
       </c>
       <c r="B14" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="C14">
-        <v>14900</v>
+        <v>10000</v>
       </c>
       <c r="D14" t="s">
-        <v>3682</v>
+        <v>3673</v>
       </c>
       <c r="E14">
-        <v>12700</v>
+        <v>8500</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="s">
         <v>3495</v>
@@ -12462,22 +12465,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>3993</v>
+        <v>3994</v>
       </c>
       <c r="B15" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="C15">
-        <v>54540</v>
+        <v>14900</v>
       </c>
       <c r="D15" t="s">
         <v>3682</v>
       </c>
       <c r="E15">
-        <v>46400</v>
+        <v>12700</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="s">
         <v>3495</v>
@@ -12485,22 +12488,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>3992</v>
+        <v>3993</v>
       </c>
       <c r="B16" t="s">
-        <v>3719</v>
+        <v>3718</v>
       </c>
       <c r="C16">
-        <v>35700</v>
+        <v>54540</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>3682</v>
       </c>
       <c r="E16">
-        <v>30300</v>
+        <v>46400</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" t="s">
         <v>3495</v>
@@ -12508,22 +12511,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>3991</v>
+        <v>3992</v>
       </c>
       <c r="B17" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="C17">
-        <v>12500</v>
+        <v>35700</v>
       </c>
       <c r="D17" t="s">
-        <v>3682</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>10600</v>
+        <v>30300</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="s">
         <v>3495</v>
@@ -12531,22 +12534,22 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>3990</v>
+        <v>3991</v>
       </c>
       <c r="B18" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="C18">
-        <v>66000</v>
+        <v>12500</v>
       </c>
       <c r="D18" t="s">
         <v>3682</v>
       </c>
       <c r="E18">
-        <v>56100</v>
+        <v>10600</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
         <v>3495</v>
@@ -12554,19 +12557,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>3989</v>
+        <v>3990</v>
       </c>
       <c r="B19" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="C19">
-        <v>9800</v>
+        <v>66000</v>
       </c>
       <c r="D19" t="s">
-        <v>3673</v>
+        <v>3682</v>
       </c>
       <c r="E19">
-        <v>8300</v>
+        <v>56100</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -12577,22 +12580,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>3988</v>
+        <v>3989</v>
       </c>
       <c r="B20" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="C20">
-        <v>38800</v>
+        <v>9800</v>
       </c>
       <c r="D20" t="s">
         <v>3673</v>
       </c>
       <c r="E20">
-        <v>33000</v>
+        <v>8300</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" t="s">
         <v>3495</v>
@@ -12600,22 +12603,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>3987</v>
+        <v>3988</v>
       </c>
       <c r="B21" t="s">
-        <v>3711</v>
+        <v>3723</v>
       </c>
       <c r="C21">
-        <v>8000</v>
+        <v>38800</v>
       </c>
       <c r="D21" t="s">
-        <v>3472</v>
+        <v>3673</v>
       </c>
       <c r="E21">
-        <v>6800</v>
+        <v>33000</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
         <v>3495</v>
@@ -12623,22 +12626,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3986</v>
+        <v>3987</v>
       </c>
       <c r="B22" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="C22">
-        <v>28520</v>
+        <v>8000</v>
       </c>
       <c r="D22" t="s">
-        <v>3685</v>
+        <v>3472</v>
       </c>
       <c r="E22">
-        <v>24200</v>
+        <v>6800</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="s">
         <v>3495</v>
@@ -12646,19 +12649,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>3985</v>
+        <v>3986</v>
       </c>
       <c r="B23" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="C23">
-        <v>40000</v>
+        <v>28520</v>
       </c>
       <c r="D23" t="s">
-        <v>3678</v>
+        <v>3685</v>
       </c>
       <c r="E23">
-        <v>34000</v>
+        <v>24200</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -12669,22 +12672,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="B24" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="C24">
-        <v>21760</v>
+        <v>40000</v>
       </c>
       <c r="D24" t="s">
-        <v>3469</v>
+        <v>3678</v>
       </c>
       <c r="E24">
-        <v>18500</v>
+        <v>34000</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="s">
         <v>3495</v>
@@ -12692,19 +12695,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3983</v>
+        <v>3984</v>
       </c>
       <c r="B25" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="C25">
-        <v>38060</v>
+        <v>21760</v>
       </c>
       <c r="D25" t="s">
-        <v>3676</v>
+        <v>3469</v>
       </c>
       <c r="E25">
-        <v>32400</v>
+        <v>18500</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -12715,22 +12718,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3982</v>
+        <v>3983</v>
       </c>
       <c r="B26" t="s">
-        <v>3671</v>
+        <v>3715</v>
       </c>
       <c r="C26">
-        <v>13970</v>
+        <v>38060</v>
       </c>
       <c r="D26" t="s">
-        <v>3476</v>
+        <v>3676</v>
       </c>
       <c r="E26">
-        <v>11900</v>
+        <v>32400</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="s">
         <v>3495</v>
@@ -12738,22 +12741,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>3981</v>
+        <v>3982</v>
       </c>
       <c r="B27" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="C27">
-        <v>10590</v>
+        <v>13970</v>
       </c>
       <c r="D27" t="s">
-        <v>3673</v>
+        <v>3476</v>
       </c>
       <c r="E27">
-        <v>9000</v>
+        <v>11900</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="s">
         <v>3495</v>
@@ -12761,19 +12764,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>3980</v>
+        <v>3981</v>
       </c>
       <c r="B28" t="s">
-        <v>3666</v>
+        <v>3672</v>
       </c>
       <c r="C28">
-        <v>135290</v>
+        <v>10590</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>3673</v>
       </c>
       <c r="E28">
-        <v>115000</v>
+        <v>9000</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -12784,19 +12787,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>3979</v>
+        <v>3980</v>
       </c>
       <c r="B29" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="C29">
-        <v>55300</v>
+        <v>135290</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E29">
-        <v>47000</v>
+        <v>115000</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -12807,19 +12810,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>3978</v>
+        <v>3979</v>
       </c>
       <c r="B30" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="C30">
-        <v>30650</v>
+        <v>55300</v>
       </c>
       <c r="D30" t="s">
-        <v>3471</v>
+        <v>26</v>
       </c>
       <c r="E30">
-        <v>26100</v>
+        <v>47000</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -12830,22 +12833,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>3977</v>
+        <v>3978</v>
       </c>
       <c r="B31" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="C31">
-        <v>30800</v>
+        <v>30650</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>3471</v>
       </c>
       <c r="E31">
-        <v>26200</v>
+        <v>26100</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="s">
         <v>3495</v>
@@ -12853,19 +12856,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>3976</v>
+        <v>3977</v>
       </c>
       <c r="B32" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="C32">
-        <v>6470</v>
+        <v>30800</v>
       </c>
       <c r="D32" t="s">
-        <v>3673</v>
+        <v>25</v>
       </c>
       <c r="E32">
-        <v>5500</v>
+        <v>26200</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -12876,22 +12879,22 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>3975</v>
+        <v>3976</v>
       </c>
       <c r="B33" t="s">
-        <v>3652</v>
+        <v>3670</v>
       </c>
       <c r="C33">
-        <v>3530</v>
+        <v>6470</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>3673</v>
       </c>
       <c r="E33">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="s">
         <v>3495</v>
@@ -12899,22 +12902,22 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>3974</v>
+        <v>3975</v>
       </c>
       <c r="B34" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="C34">
-        <v>9500</v>
+        <v>3530</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E34">
-        <v>8100</v>
+        <v>3000</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
         <v>3495</v>
@@ -12922,22 +12925,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>3973</v>
+        <v>3974</v>
       </c>
       <c r="B35" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="C35">
-        <v>31770</v>
+        <v>9500</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E35">
-        <v>27000</v>
+        <v>8100</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="s">
         <v>3495</v>
@@ -12945,22 +12948,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="B36" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="C36">
-        <v>10590</v>
+        <v>31770</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" t="s">
         <v>3495</v>
@@ -12968,22 +12971,22 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>3971</v>
+        <v>3972</v>
       </c>
       <c r="B37" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="C37">
-        <v>9650</v>
+        <v>10590</v>
       </c>
       <c r="D37" t="s">
         <v>32</v>
       </c>
       <c r="E37">
-        <v>8200</v>
+        <v>9000</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G37" t="s">
         <v>3495</v>
@@ -12991,22 +12994,22 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3970</v>
+        <v>3971</v>
       </c>
       <c r="B38" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="C38">
-        <v>10590</v>
+        <v>9650</v>
       </c>
       <c r="D38" t="s">
         <v>32</v>
       </c>
       <c r="E38">
-        <v>9000</v>
+        <v>8200</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G38" t="s">
         <v>3495</v>
@@ -13014,22 +13017,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>3969</v>
+        <v>3970</v>
       </c>
       <c r="B39" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C39">
-        <v>4120</v>
+        <v>10590</v>
       </c>
       <c r="D39" t="s">
-        <v>3484</v>
+        <v>32</v>
       </c>
       <c r="E39">
-        <v>3500</v>
+        <v>9000</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G39" t="s">
         <v>3495</v>
@@ -13037,22 +13040,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>3968</v>
+        <v>3969</v>
       </c>
       <c r="B40" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="C40">
-        <v>28240</v>
+        <v>4120</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>3484</v>
       </c>
       <c r="E40">
-        <v>24000</v>
+        <v>3500</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G40" t="s">
         <v>3495</v>
@@ -13060,19 +13063,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>3967</v>
+        <v>3968</v>
       </c>
       <c r="B41" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="C41">
-        <v>23530</v>
+        <v>28240</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E41">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -13083,22 +13086,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3966</v>
+        <v>3967</v>
       </c>
       <c r="B42" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="C42">
-        <v>30700</v>
+        <v>23530</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E42">
-        <v>26100</v>
+        <v>20000</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s">
         <v>3495</v>
@@ -13106,22 +13109,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>3965</v>
+        <v>3966</v>
       </c>
       <c r="B43" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="C43">
-        <v>16100</v>
+        <v>30700</v>
       </c>
       <c r="D43" t="s">
-        <v>3673</v>
+        <v>32</v>
       </c>
       <c r="E43">
-        <v>13700</v>
+        <v>26100</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" t="s">
         <v>3495</v>
@@ -13129,22 +13132,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="B44" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="C44">
-        <v>27750</v>
+        <v>16100</v>
       </c>
       <c r="D44" t="s">
-        <v>3602</v>
+        <v>3673</v>
       </c>
       <c r="E44">
-        <v>23600</v>
+        <v>13700</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" t="s">
         <v>3495</v>
@@ -13152,19 +13155,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="B45" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="C45">
-        <v>32000</v>
+        <v>27750</v>
       </c>
       <c r="D45" t="s">
         <v>3602</v>
       </c>
       <c r="E45">
-        <v>27200</v>
+        <v>23600</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -13175,19 +13178,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="B46" t="s">
-        <v>3646</v>
+        <v>3664</v>
       </c>
       <c r="C46">
-        <v>3600</v>
+        <v>32000</v>
       </c>
       <c r="D46" t="s">
-        <v>33</v>
+        <v>3602</v>
       </c>
       <c r="E46">
-        <v>3100</v>
+        <v>27200</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -13198,22 +13201,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>3961</v>
+        <v>3962</v>
       </c>
       <c r="B47" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="C47">
-        <v>44700</v>
+        <v>3600</v>
       </c>
       <c r="D47" t="s">
-        <v>3477</v>
+        <v>33</v>
       </c>
       <c r="E47">
-        <v>38000</v>
+        <v>3100</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="s">
         <v>3495</v>
@@ -13221,22 +13224,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>3960</v>
+        <v>3961</v>
       </c>
       <c r="B48" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="C48">
-        <v>24120</v>
+        <v>44700</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>3477</v>
       </c>
       <c r="E48">
-        <v>20500</v>
+        <v>38000</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="s">
         <v>3495</v>
@@ -13244,22 +13247,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>3959</v>
+        <v>3960</v>
       </c>
       <c r="B49" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="C49">
-        <v>11250</v>
+        <v>24120</v>
       </c>
       <c r="D49" t="s">
-        <v>3475</v>
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>9600</v>
+        <v>20500</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="s">
         <v>3495</v>
@@ -13267,22 +13270,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="B50" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="C50">
-        <v>5880</v>
+        <v>11250</v>
       </c>
       <c r="D50" t="s">
-        <v>3482</v>
+        <v>3475</v>
       </c>
       <c r="E50">
-        <v>5000</v>
+        <v>9600</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G50" t="s">
         <v>3495</v>
@@ -13290,22 +13293,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>3957</v>
+        <v>3958</v>
       </c>
       <c r="B51" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="C51">
-        <v>4120</v>
+        <v>5880</v>
       </c>
       <c r="D51" t="s">
         <v>3482</v>
       </c>
       <c r="E51">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" t="s">
         <v>3495</v>
@@ -13313,22 +13316,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>3956</v>
+        <v>3957</v>
       </c>
       <c r="B52" t="s">
-        <v>3638</v>
+        <v>3651</v>
       </c>
       <c r="C52">
-        <v>57650</v>
+        <v>4120</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
+        <v>3482</v>
       </c>
       <c r="E52">
-        <v>49000</v>
+        <v>3500</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G52" t="s">
         <v>3495</v>
@@ -13336,45 +13339,45 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>3955</v>
+        <v>3956</v>
       </c>
       <c r="B53" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="C53">
-        <v>12000</v>
+        <v>57650</v>
       </c>
       <c r="D53" t="s">
-        <v>3673</v>
+        <v>28</v>
       </c>
       <c r="E53">
-        <v>10200</v>
+        <v>49000</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>3954</v>
+        <v>3955</v>
       </c>
       <c r="B54" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="C54">
-        <v>2350</v>
+        <v>12000</v>
       </c>
       <c r="D54" t="s">
-        <v>3468</v>
+        <v>3673</v>
       </c>
       <c r="E54">
-        <v>2000</v>
+        <v>10200</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G54" t="s">
         <v>3495</v>
@@ -13382,42 +13385,42 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>3953</v>
+        <v>3954</v>
       </c>
       <c r="B55" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="C55">
-        <v>63530</v>
+        <v>2350</v>
       </c>
       <c r="D55" t="s">
-        <v>3478</v>
+        <v>3468</v>
       </c>
       <c r="E55">
-        <v>54000</v>
+        <v>2000</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>3952</v>
+        <v>3953</v>
       </c>
       <c r="B56" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="C56">
-        <v>10590</v>
+        <v>63530</v>
       </c>
       <c r="D56" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="E56">
-        <v>9000</v>
+        <v>54000</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -13428,68 +13431,68 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>3951</v>
+        <v>3952</v>
       </c>
       <c r="B57" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="C57">
-        <v>20350</v>
+        <v>10590</v>
       </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>3480</v>
       </c>
       <c r="E57">
-        <v>17300</v>
+        <v>9000</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>3950</v>
+        <v>3951</v>
       </c>
       <c r="B58" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="C58">
-        <v>8240</v>
+        <v>20350</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58">
-        <v>7000</v>
+        <v>17300</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>3949</v>
+        <v>3950</v>
       </c>
       <c r="B59" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="C59">
-        <v>18600</v>
+        <v>8240</v>
       </c>
       <c r="D59" t="s">
-        <v>3480</v>
+        <v>26</v>
       </c>
       <c r="E59">
-        <v>15800</v>
+        <v>7000</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="s">
         <v>3495</v>
@@ -13497,19 +13500,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c r="B60" t="s">
-        <v>3627</v>
+        <v>3645</v>
       </c>
       <c r="C60">
-        <v>105880</v>
+        <v>18600</v>
       </c>
       <c r="D60" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="E60">
-        <v>90000</v>
+        <v>15800</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -13520,22 +13523,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="B61" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="C61">
-        <v>77000</v>
+        <v>105880</v>
       </c>
       <c r="D61" t="s">
-        <v>3486</v>
+        <v>3479</v>
       </c>
       <c r="E61">
-        <v>65500</v>
+        <v>90000</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="s">
         <v>3495</v>
@@ -13543,19 +13546,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>3946</v>
+        <v>3947</v>
       </c>
       <c r="B62" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="C62">
-        <v>14400</v>
+        <v>77000</v>
       </c>
       <c r="D62" t="s">
-        <v>3479</v>
+        <v>3486</v>
       </c>
       <c r="E62">
-        <v>12200</v>
+        <v>65500</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -13566,22 +13569,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="B63" t="s">
-        <v>3665</v>
+        <v>3629</v>
       </c>
       <c r="C63">
-        <v>24700</v>
+        <v>14400</v>
       </c>
       <c r="D63" t="s">
-        <v>3469</v>
+        <v>3479</v>
       </c>
       <c r="E63">
-        <v>21000</v>
+        <v>12200</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="s">
         <v>3495</v>
@@ -13589,22 +13592,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>3944</v>
+        <v>3945</v>
       </c>
       <c r="B64" t="s">
-        <v>3630</v>
+        <v>3665</v>
       </c>
       <c r="C64">
-        <v>24000</v>
+        <v>24700</v>
       </c>
       <c r="D64" t="s">
         <v>3469</v>
       </c>
       <c r="E64">
-        <v>20400</v>
+        <v>21000</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="s">
         <v>3495</v>
@@ -13612,22 +13615,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>3943</v>
+        <v>3944</v>
       </c>
       <c r="B65" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="C65">
-        <v>18820</v>
+        <v>24000</v>
       </c>
       <c r="D65" t="s">
-        <v>33</v>
+        <v>3469</v>
       </c>
       <c r="E65">
-        <v>16000</v>
+        <v>20400</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="s">
         <v>3495</v>
@@ -13635,22 +13638,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="B66" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="C66">
-        <v>20000</v>
+        <v>18820</v>
       </c>
       <c r="D66" t="s">
-        <v>3469</v>
+        <v>33</v>
       </c>
       <c r="E66">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G66" t="s">
         <v>3495</v>
@@ -13658,22 +13661,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>3941</v>
+        <v>3942</v>
       </c>
       <c r="B67" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="C67">
-        <v>45880</v>
+        <v>20000</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>3469</v>
       </c>
       <c r="E67">
-        <v>39000</v>
+        <v>17000</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G67" t="s">
         <v>3495</v>
@@ -13681,22 +13684,22 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="B68" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="C68">
-        <v>20590</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E68">
-        <v>17500</v>
+        <v>39000</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G68" t="s">
         <v>3495</v>
@@ -13704,19 +13707,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>3939</v>
+        <v>3940</v>
       </c>
       <c r="B69" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="C69">
-        <v>10590</v>
+        <v>20590</v>
       </c>
       <c r="D69" t="s">
-        <v>3474</v>
+        <v>25</v>
       </c>
       <c r="E69">
-        <v>9000</v>
+        <v>17500</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -13727,22 +13730,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="B70" t="s">
-        <v>3621</v>
+        <v>3635</v>
       </c>
       <c r="C70">
-        <v>20000</v>
+        <v>10590</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>3474</v>
       </c>
       <c r="E70">
-        <v>17000</v>
+        <v>9000</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="s">
         <v>3495</v>
@@ -13750,94 +13753,94 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="B71" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="C71">
-        <v>13600</v>
+        <v>20000</v>
       </c>
       <c r="D71" t="s">
-        <v>3470</v>
+        <v>25</v>
       </c>
       <c r="E71">
-        <v>11600</v>
+        <v>17000</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="B72" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="C72">
-        <v>13970</v>
+        <v>13600</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>3470</v>
       </c>
       <c r="E72">
-        <v>11900</v>
+        <v>11600</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>3935</v>
+        <v>3936</v>
       </c>
       <c r="B73" t="s">
-        <v>3616</v>
+        <v>3623</v>
       </c>
       <c r="C73">
-        <v>16000</v>
+        <v>13970</v>
       </c>
       <c r="D73" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E73">
-        <v>13600</v>
+        <v>11900</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>3934</v>
+        <v>3935</v>
       </c>
       <c r="B74" t="s">
-        <v>3511</v>
+        <v>3616</v>
       </c>
       <c r="C74">
-        <v>31500</v>
+        <v>16000</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E74">
-        <v>26800</v>
+        <v>13600</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -13883,7 +13886,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -13940,19 +13943,19 @@
         <v>3620</v>
       </c>
       <c r="C79">
-        <v>35900</v>
+        <v>34705</v>
       </c>
       <c r="D79" t="s">
         <v>3674</v>
       </c>
       <c r="E79">
-        <v>30500</v>
+        <v>29500</v>
       </c>
       <c r="F79">
         <v>4</v>
       </c>
       <c r="G79" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -14159,7 +14162,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -14202,10 +14205,10 @@
         <v>19000</v>
       </c>
       <c r="F90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -14343,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -15067,19 +15070,19 @@
         <v>44</v>
       </c>
       <c r="C128">
-        <v>31100</v>
+        <v>32940</v>
       </c>
       <c r="D128" t="s">
         <v>3470</v>
       </c>
       <c r="E128">
-        <v>26400</v>
+        <v>28000</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -15421,7 +15424,7 @@
         <v>25800</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="s">
         <v>3495</v>
@@ -15973,7 +15976,7 @@
         <v>4700</v>
       </c>
       <c r="F167">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G167" t="s">
         <v>3495</v>
@@ -17856,7 +17859,7 @@
         <v>19500</v>
       </c>
       <c r="F249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G249" t="s">
         <v>3496</v>
@@ -19006,7 +19009,7 @@
         <v>29500</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" t="s">
         <v>3496</v>
@@ -21148,7 +21151,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -48124,7 +48127,7 @@
         <v>14200</v>
       </c>
       <c r="F1565">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1565" t="s">
         <v>3495</v>
@@ -48239,7 +48242,7 @@
         <v>1100</v>
       </c>
       <c r="F1570">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1570" t="s">
         <v>3495</v>
@@ -48817,7 +48820,7 @@
         <v>0</v>
       </c>
       <c r="G1595" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="1596" spans="1:7" x14ac:dyDescent="0.25">
@@ -55530,10 +55533,10 @@
         <v>22600</v>
       </c>
       <c r="F1887">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1887" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="1888" spans="1:7" x14ac:dyDescent="0.25">
@@ -55737,7 +55740,7 @@
         <v>16900</v>
       </c>
       <c r="F1896">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1896" t="s">
         <v>3495</v>
@@ -57580,7 +57583,7 @@
         <v>0</v>
       </c>
       <c r="G1976" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="1977" spans="1:7" x14ac:dyDescent="0.25">
@@ -59785,7 +59788,7 @@
         <v>3900</v>
       </c>
       <c r="F2072">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2072" t="s">
         <v>3495</v>
@@ -63557,7 +63560,7 @@
         <v>6500</v>
       </c>
       <c r="F2236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2236" t="s">
         <v>3495</v>
@@ -64339,7 +64342,7 @@
         <v>45500</v>
       </c>
       <c r="F2270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2270" t="s">
         <v>3495</v>
@@ -66573,7 +66576,7 @@
         <v>0</v>
       </c>
       <c r="G2367" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="2368" spans="1:7" x14ac:dyDescent="0.25">
@@ -67237,7 +67240,7 @@
         <v>11800</v>
       </c>
       <c r="F2396">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2396" t="s">
         <v>3495</v>
@@ -70963,7 +70966,7 @@
         <v>56400</v>
       </c>
       <c r="F2558">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2558" t="s">
         <v>3495</v>
@@ -71584,7 +71587,7 @@
         <v>38000</v>
       </c>
       <c r="F2585">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2585" t="s">
         <v>3495</v>
@@ -74899,7 +74902,7 @@
         <v>1</v>
       </c>
       <c r="G2729" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="2730" spans="1:7" x14ac:dyDescent="0.25">
@@ -75658,7 +75661,7 @@
         <v>1</v>
       </c>
       <c r="G2762" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="2763" spans="1:7" x14ac:dyDescent="0.25">
@@ -79059,7 +79062,7 @@
         <v>17000</v>
       </c>
       <c r="F2910">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2910" t="s">
         <v>3496</v>
@@ -84763,7 +84766,7 @@
         <v>17600</v>
       </c>
       <c r="F3158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3158" t="s">
         <v>3495</v>
@@ -88374,7 +88377,7 @@
         <v>44500</v>
       </c>
       <c r="F3315">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3315" t="s">
         <v>3495</v>
@@ -90076,7 +90079,7 @@
         <v>600</v>
       </c>
       <c r="F3389">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3389" t="s">
         <v>3495</v>
@@ -90605,7 +90608,7 @@
         <v>1000</v>
       </c>
       <c r="F3412">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3412" t="s">
         <v>3495</v>
@@ -90858,7 +90861,7 @@
         <v>2700</v>
       </c>
       <c r="F3423">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3423" t="s">
         <v>3495</v>
@@ -92123,7 +92126,7 @@
         <v>1900</v>
       </c>
       <c r="F3478">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3478" t="s">
         <v>3495</v>
@@ -95665,7 +95668,7 @@
         <v>9000</v>
       </c>
       <c r="F3632">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3632" t="s">
         <v>3495</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE00F9CC-4182-410B-BCDE-E28DD43CDDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BAAEFA-0B65-4D9C-8F56-D4AFB42D5D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1842708-B93E-4B19-8BFC-231BBDD6ED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229E8538-7456-441E-B433-B0DA21BD6791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>
@@ -12314,7 +12314,7 @@
         <v>28900</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>3494</v>
@@ -12406,7 +12406,7 @@
         <v>21300</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
         <v>3494</v>
@@ -12452,7 +12452,7 @@
         <v>3500</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="s">
         <v>3494</v>
@@ -12682,7 +12682,7 @@
         <v>30300</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
         <v>3494</v>
@@ -13165,7 +13165,7 @@
         <v>8200</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44" t="s">
         <v>3494</v>
@@ -13211,7 +13211,7 @@
         <v>3500</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46" t="s">
         <v>3494</v>
@@ -13720,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -13743,7 +13743,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -13927,7 +13927,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14085,7 +14085,7 @@
         <v>23000</v>
       </c>
       <c r="F84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" t="s">
         <v>3494</v>
@@ -14226,7 +14226,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -15373,7 +15373,7 @@
         <v>27800</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="s">
         <v>3494</v>
@@ -15810,7 +15810,7 @@
         <v>8800</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G159" t="s">
         <v>3494</v>
@@ -16434,7 +16434,7 @@
         <v>3</v>
       </c>
       <c r="G186" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -17716,7 +17716,7 @@
         <v>20500</v>
       </c>
       <c r="F242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G242" t="s">
         <v>3494</v>
@@ -18383,7 +18383,7 @@
         <v>27000</v>
       </c>
       <c r="F271">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G271" t="s">
         <v>3494</v>
@@ -24688,7 +24688,7 @@
         <v>0</v>
       </c>
       <c r="G545" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -27353,7 +27353,7 @@
         <v>16300</v>
       </c>
       <c r="F661">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G661" t="s">
         <v>3495</v>
@@ -27721,7 +27721,7 @@
         <v>24500</v>
       </c>
       <c r="F677">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G677" t="s">
         <v>3494</v>
@@ -35587,7 +35587,7 @@
         <v>11800</v>
       </c>
       <c r="F1019">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1019" t="s">
         <v>3494</v>
@@ -35702,7 +35702,7 @@
         <v>20000</v>
       </c>
       <c r="F1024">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1024" t="s">
         <v>3494</v>
@@ -38370,7 +38370,7 @@
         <v>3500</v>
       </c>
       <c r="F1140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1140" t="s">
         <v>3494</v>
@@ -38577,7 +38577,7 @@
         <v>27500</v>
       </c>
       <c r="F1149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1149" t="s">
         <v>3494</v>
@@ -43706,10 +43706,10 @@
         <v>20500</v>
       </c>
       <c r="F1372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1372" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
@@ -44143,7 +44143,7 @@
         <v>3500</v>
       </c>
       <c r="F1391">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1391" t="s">
         <v>3494</v>
@@ -45040,7 +45040,7 @@
         <v>31900</v>
       </c>
       <c r="F1430">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1430" t="s">
         <v>3494</v>
@@ -45089,7 +45089,7 @@
         <v>3</v>
       </c>
       <c r="G1432" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.25">
@@ -45178,7 +45178,7 @@
         <v>30900</v>
       </c>
       <c r="F1436">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1436" t="s">
         <v>3495</v>
@@ -48076,7 +48076,7 @@
         <v>76000</v>
       </c>
       <c r="F1562">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1562" t="s">
         <v>3494</v>
@@ -48835,7 +48835,7 @@
         <v>70200</v>
       </c>
       <c r="F1595">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G1595" t="s">
         <v>3495</v>
@@ -49479,7 +49479,7 @@
         <v>22000</v>
       </c>
       <c r="F1623">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1623" t="s">
         <v>3494</v>
@@ -49640,7 +49640,7 @@
         <v>20400</v>
       </c>
       <c r="F1630">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1630" t="s">
         <v>3494</v>
@@ -55827,7 +55827,7 @@
         <v>10500</v>
       </c>
       <c r="F1899">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1899" t="s">
         <v>3494</v>
@@ -56747,7 +56747,7 @@
         <v>10400</v>
       </c>
       <c r="F1939">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1939" t="s">
         <v>3494</v>
@@ -57713,7 +57713,7 @@
         <v>14800</v>
       </c>
       <c r="F1981">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1981" t="s">
         <v>3495</v>
@@ -58426,7 +58426,7 @@
         <v>5800</v>
       </c>
       <c r="F2012">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2012" t="s">
         <v>3494</v>
@@ -59162,7 +59162,7 @@
         <v>12800</v>
       </c>
       <c r="F2044">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2044" t="s">
         <v>3494</v>
@@ -59691,7 +59691,7 @@
         <v>16800</v>
       </c>
       <c r="F2067">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2067" t="s">
         <v>3494</v>
@@ -61557,7 +61557,7 @@
         <v>0</v>
       </c>
       <c r="G2148" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="2149" spans="1:7" x14ac:dyDescent="0.25">
@@ -62290,7 +62290,7 @@
         <v>4000</v>
       </c>
       <c r="F2180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2180" t="s">
         <v>3495</v>
@@ -63693,7 +63693,7 @@
         <v>6500</v>
       </c>
       <c r="F2241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2241" t="s">
         <v>3494</v>
@@ -64107,7 +64107,7 @@
         <v>10200</v>
       </c>
       <c r="F2259">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2259" t="s">
         <v>3494</v>
@@ -66982,7 +66982,7 @@
         <v>9000</v>
       </c>
       <c r="F2384">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2384" t="s">
         <v>3494</v>
@@ -73951,7 +73951,7 @@
         <v>10600</v>
       </c>
       <c r="F2687">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2687" t="s">
         <v>3494</v>
@@ -74204,7 +74204,7 @@
         <v>14600</v>
       </c>
       <c r="F2698">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2698" t="s">
         <v>3494</v>
@@ -88947,7 +88947,7 @@
         <v>22700</v>
       </c>
       <c r="F3339">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3339" t="s">
         <v>3495</v>
@@ -90143,7 +90143,7 @@
         <v>3300</v>
       </c>
       <c r="F3391">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3391" t="s">
         <v>3494</v>
@@ -90212,7 +90212,7 @@
         <v>600</v>
       </c>
       <c r="F3394">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G3394" t="s">
         <v>3494</v>
@@ -90419,7 +90419,7 @@
         <v>2500</v>
       </c>
       <c r="F3403">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3403" t="s">
         <v>3494</v>
@@ -94007,7 +94007,7 @@
         <v>19200</v>
       </c>
       <c r="F3559">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3559" t="s">
         <v>3495</v>
@@ -94674,7 +94674,7 @@
         <v>7600</v>
       </c>
       <c r="F3588">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3588" t="s">
         <v>3494</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229E8538-7456-441E-B433-B0DA21BD6791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB020219-8E84-4DEA-AE9A-13EC29FA2BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11029" uniqueCount="3746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11029" uniqueCount="3747">
   <si>
     <t>CODIGO</t>
   </si>
@@ -11272,6 +11272,9 @@
   </si>
   <si>
     <t>Mochilas/bolsos</t>
+  </si>
+  <si>
+    <t>Electricidad</t>
   </si>
 </sst>
 </file>
@@ -12452,7 +12455,7 @@
         <v>3500</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
         <v>3494</v>
@@ -12561,7 +12564,7 @@
         <v>25000</v>
       </c>
       <c r="D18" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E18">
         <v>21300</v>
@@ -12607,7 +12610,7 @@
         <v>10000</v>
       </c>
       <c r="D20" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E20">
         <v>8500</v>
@@ -12745,7 +12748,7 @@
         <v>9800</v>
       </c>
       <c r="D26" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E26">
         <v>8300</v>
@@ -12768,7 +12771,7 @@
         <v>38800</v>
       </c>
       <c r="D27" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E27">
         <v>33000</v>
@@ -12929,7 +12932,7 @@
         <v>10590</v>
       </c>
       <c r="D34" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E34">
         <v>9000</v>
@@ -13044,7 +13047,7 @@
         <v>6470</v>
       </c>
       <c r="D39" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E39">
         <v>5500</v>
@@ -13297,7 +13300,7 @@
         <v>16100</v>
       </c>
       <c r="D50" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E50">
         <v>13700</v>
@@ -13527,7 +13530,7 @@
         <v>12000</v>
       </c>
       <c r="D60" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E60">
         <v>10200</v>
@@ -14033,7 +14036,7 @@
         <v>14940</v>
       </c>
       <c r="D82" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E82">
         <v>12700</v>
@@ -14378,7 +14381,7 @@
         <v>10590</v>
       </c>
       <c r="D97" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E97">
         <v>9000</v>
@@ -14815,7 +14818,7 @@
         <v>9000</v>
       </c>
       <c r="D116" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E116">
         <v>7700</v>
@@ -15114,7 +15117,7 @@
         <v>41760</v>
       </c>
       <c r="D129" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E129">
         <v>35500</v>
@@ -15249,13 +15252,13 @@
         <v>45</v>
       </c>
       <c r="C135">
-        <v>29100</v>
+        <v>31040</v>
       </c>
       <c r="D135" t="s">
         <v>3469</v>
       </c>
       <c r="E135">
-        <v>24700</v>
+        <v>26400</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -15781,7 +15784,7 @@
         <v>13430</v>
       </c>
       <c r="D158" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E158">
         <v>11400</v>
@@ -16724,7 +16727,7 @@
         <v>5100</v>
       </c>
       <c r="D199" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E199">
         <v>4300</v>
@@ -17023,7 +17026,7 @@
         <v>10830</v>
       </c>
       <c r="D212" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E212">
         <v>9200</v>
@@ -17506,7 +17509,7 @@
         <v>16470</v>
       </c>
       <c r="D233" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E233">
         <v>14000</v>
@@ -17598,7 +17601,7 @@
         <v>22300</v>
       </c>
       <c r="D237" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E237">
         <v>19000</v>
@@ -17779,7 +17782,7 @@
         <v>13000</v>
       </c>
       <c r="D245" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E245">
         <v>11100</v>
@@ -18492,7 +18495,7 @@
         <v>11000</v>
       </c>
       <c r="D276" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E276">
         <v>9400</v>
@@ -19136,7 +19139,7 @@
         <v>34700</v>
       </c>
       <c r="D304" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E304">
         <v>29500</v>
@@ -19320,7 +19323,7 @@
         <v>24300</v>
       </c>
       <c r="D312" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E312">
         <v>20700</v>
@@ -19412,7 +19415,7 @@
         <v>6600</v>
       </c>
       <c r="D316" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E316">
         <v>5600</v>
@@ -19435,7 +19438,7 @@
         <v>28600</v>
       </c>
       <c r="D317" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E317">
         <v>24300</v>
@@ -19458,7 +19461,7 @@
         <v>6000</v>
       </c>
       <c r="D318" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E318">
         <v>5100</v>
@@ -19481,7 +19484,7 @@
         <v>18820</v>
       </c>
       <c r="D319" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E319">
         <v>16000</v>
@@ -19527,7 +19530,7 @@
         <v>23300</v>
       </c>
       <c r="D321" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E321">
         <v>19800</v>
@@ -20286,7 +20289,7 @@
         <v>18500</v>
       </c>
       <c r="D354" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E354">
         <v>15700</v>
@@ -20470,7 +20473,7 @@
         <v>7000</v>
       </c>
       <c r="D362" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E362">
         <v>6000</v>
@@ -20562,7 +20565,7 @@
         <v>23090</v>
       </c>
       <c r="D366" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E366">
         <v>19600</v>
@@ -21183,7 +21186,7 @@
         <v>38000</v>
       </c>
       <c r="D393" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E393">
         <v>32300</v>
@@ -21321,7 +21324,7 @@
         <v>23090</v>
       </c>
       <c r="D399" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E399">
         <v>19600</v>
@@ -21344,7 +21347,7 @@
         <v>18000</v>
       </c>
       <c r="D400" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E400">
         <v>15300</v>
@@ -21390,7 +21393,7 @@
         <v>23090</v>
       </c>
       <c r="D402" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E402">
         <v>19600</v>
@@ -21413,7 +21416,7 @@
         <v>23090</v>
       </c>
       <c r="D403" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E403">
         <v>19600</v>
@@ -21436,7 +21439,7 @@
         <v>23060</v>
       </c>
       <c r="D404" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E404">
         <v>19600</v>
@@ -21459,7 +21462,7 @@
         <v>23090</v>
       </c>
       <c r="D405" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E405">
         <v>19600</v>
@@ -21482,7 +21485,7 @@
         <v>23090</v>
       </c>
       <c r="D406" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E406">
         <v>19600</v>
@@ -21505,7 +21508,7 @@
         <v>23060</v>
       </c>
       <c r="D407" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E407">
         <v>19600</v>
@@ -22034,7 +22037,7 @@
         <v>28510</v>
       </c>
       <c r="D430" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E430">
         <v>24200</v>
@@ -22172,7 +22175,7 @@
         <v>12690</v>
       </c>
       <c r="D436" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E436">
         <v>10800</v>
@@ -22195,7 +22198,7 @@
         <v>22940</v>
       </c>
       <c r="D437" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E437">
         <v>19500</v>
@@ -22264,7 +22267,7 @@
         <v>3310</v>
       </c>
       <c r="D440" t="s">
-        <v>3672</v>
+        <v>3485</v>
       </c>
       <c r="E440">
         <v>2800</v>
@@ -23736,7 +23739,7 @@
         <v>16230</v>
       </c>
       <c r="D504" t="s">
-        <v>3672</v>
+        <v>3746</v>
       </c>
       <c r="E504">
         <v>13800</v>
@@ -43559,13 +43562,13 @@
         <v>1229</v>
       </c>
       <c r="C1366">
-        <v>10400</v>
+        <v>10590</v>
       </c>
       <c r="D1366" t="s">
         <v>3686</v>
       </c>
       <c r="E1366">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="F1366">
         <v>6</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Pagina Web Tecnocodys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB020219-8E84-4DEA-AE9A-13EC29FA2BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E215D858-907B-46B1-B96A-2C5C9448BC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D6650EB6-C58A-4F11-A148-31C065CE3CEC}"/>
   </bookViews>
@@ -12409,7 +12409,7 @@
         <v>21300</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="s">
         <v>3494</v>
@@ -12777,7 +12777,7 @@
         <v>33000</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="s">
         <v>3494</v>
@@ -13168,7 +13168,7 @@
         <v>8200</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44" t="s">
         <v>3494</v>
@@ -15238,7 +15238,7 @@
         <v>28000</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="s">
         <v>3494</v>
@@ -15261,7 +15261,7 @@
         <v>26400</v>
       </c>
       <c r="F135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G135" t="s">
         <v>3494</v>
@@ -19444,7 +19444,7 @@
         <v>24300</v>
       </c>
       <c r="F317">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G317" t="s">
         <v>3495</v>
@@ -21008,7 +21008,7 @@
         <v>18500</v>
       </c>
       <c r="F385">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G385" t="s">
         <v>3495</v>
@@ -22871,7 +22871,7 @@
         <v>8800</v>
       </c>
       <c r="F466">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G466" t="s">
         <v>3495</v>
@@ -25415,19 +25415,19 @@
         <v>462</v>
       </c>
       <c r="C577">
-        <v>29410</v>
+        <v>28000</v>
       </c>
       <c r="D577" t="s">
         <v>30</v>
       </c>
       <c r="E577">
-        <v>25000</v>
+        <v>23800</v>
       </c>
       <c r="F577">
         <v>0</v>
       </c>
       <c r="G577" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -26370,7 +26370,7 @@
         <v>2</v>
       </c>
       <c r="G618" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -39089,7 +39089,7 @@
         <v>0</v>
       </c>
       <c r="G1171" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="1172" spans="1:7" x14ac:dyDescent="0.25">
@@ -41018,7 +41018,7 @@
         <v>18600</v>
       </c>
       <c r="F1255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1255" t="s">
         <v>3495</v>
@@ -46472,7 +46472,7 @@
         <v>0</v>
       </c>
       <c r="G1492" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="1493" spans="1:7" x14ac:dyDescent="0.25">
@@ -50186,19 +50186,19 @@
         <v>1504</v>
       </c>
       <c r="C1654">
-        <v>25360</v>
+        <v>24470</v>
       </c>
       <c r="D1654" t="s">
         <v>24</v>
       </c>
       <c r="E1654">
-        <v>21600</v>
+        <v>20800</v>
       </c>
       <c r="F1654">
         <v>1</v>
       </c>
       <c r="G1654" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
@@ -65398,7 +65398,7 @@
         <v>10200</v>
       </c>
       <c r="F2315">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2315" t="s">
         <v>3494</v>
@@ -74414,7 +74414,7 @@
         <v>44000</v>
       </c>
       <c r="F2707">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2707" t="s">
         <v>3494</v>
@@ -81245,7 +81245,7 @@
         <v>28000</v>
       </c>
       <c r="F3004">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3004" t="s">
         <v>3494</v>
